--- a/Project4761_J. D. Pardo(2017).xlsx
+++ b/Project4761_J. D. Pardo(2017).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pjjg18\GitHub\neotrans\matrices\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pjjg18\GitHub\neotrans\inst\matrices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D95463-9D78-43B7-AD78-143709CE3F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D7412D-D79F-44DB-8D61-3794FE41723A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16455" yWindow="1170" windowWidth="15945" windowHeight="18375" xr2:uid="{E4921926-99A0-6E43-98A0-9E5C22F77220}"/>
+    <workbookView xWindow="16185" yWindow="390" windowWidth="16110" windowHeight="17460" xr2:uid="{E4921926-99A0-6E43-98A0-9E5C22F77220}"/>
   </bookViews>
   <sheets>
     <sheet name="Project4761" sheetId="1" r:id="rId1"/>
@@ -1196,7 +1196,7 @@
     <t>NT2;0=0-;1=11;2=12</t>
   </si>
   <si>
-    <t>Additive</t>
+    <t>NN;0=00;1=10;2=11</t>
   </si>
 </sst>
 </file>
